--- a/data/trans_dic/P2A_enfcro_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con enfermedades crónicas</t>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,03; 39,4</t>
+          <t>22,3; 39,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>31,33; 52,39</t>
+          <t>32,75; 52,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,42; 51,34</t>
+          <t>31,12; 51,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94,75; 99,51</t>
+          <t>94,8; 99,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,68; 44,22</t>
+          <t>25,86; 44,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,72; 45,0</t>
+          <t>25,82; 44,04</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,79; 48,06</t>
+          <t>30,54; 48,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>95,63; 99,51</t>
+          <t>95,81; 99,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,51; 38,6</t>
+          <t>26,12; 38,53</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>32,14; 46,16</t>
+          <t>30,64; 44,25</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32,54; 46,01</t>
+          <t>33,46; 47,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,63; 99,33</t>
+          <t>96,38; 99,23</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>35,1; 54,75</t>
+          <t>34,28; 54,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,03; 53,47</t>
+          <t>33,05; 52,92</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,71; 44,03</t>
+          <t>26,3; 43,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>93,27; 99,21</t>
+          <t>92,89; 99,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,85; 56,58</t>
+          <t>38,1; 56,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>36,09; 55,68</t>
+          <t>35,77; 55,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,2; 49,26</t>
+          <t>32,7; 49,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>94,46; 100,0</t>
+          <t>94,33; 100,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,55; 51,92</t>
+          <t>38,25; 52,38</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37,32; 51,33</t>
+          <t>36,98; 51,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,61; 44,94</t>
+          <t>32,98; 44,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>95,34; 99,32</t>
+          <t>95,39; 99,31</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21,35; 40,24</t>
+          <t>20,95; 40,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,23; 57,56</t>
+          <t>37,06; 56,84</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,86; 48,62</t>
+          <t>27,0; 49,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83,51; 98,41</t>
+          <t>84,08; 98,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,96; 42,94</t>
+          <t>26,74; 41,94</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,31; 50,8</t>
+          <t>31,17; 50,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,36; 47,67</t>
+          <t>28,29; 47,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89,61; 100,0</t>
+          <t>88,42; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,06; 39,39</t>
+          <t>26,2; 38,63</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36,64; 51,56</t>
+          <t>36,9; 50,85</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,46; 45,18</t>
+          <t>30,76; 45,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>89,85; 97,97</t>
+          <t>89,76; 98,15</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,43; 46,85</t>
+          <t>33,87; 47,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,54; 56,2</t>
+          <t>42,52; 55,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38,47; 51,31</t>
+          <t>39,02; 51,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94,66; 98,68</t>
+          <t>94,55; 98,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,53; 48,35</t>
+          <t>35,62; 48,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>47,1; 59,71</t>
+          <t>46,47; 59,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,64; 41,17</t>
+          <t>29,48; 41,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>90,97; 96,99</t>
+          <t>91,15; 97,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,38; 45,44</t>
+          <t>36,75; 45,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46,42; 55,64</t>
+          <t>46,58; 55,94</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,52; 44,02</t>
+          <t>35,81; 44,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,09; 97,48</t>
+          <t>93,57; 97,39</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>35,28; 54,45</t>
+          <t>34,61; 54,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,99; 52,57</t>
+          <t>35,61; 53,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,25; 53,95</t>
+          <t>38,49; 54,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>85,15; 93,64</t>
+          <t>84,0; 93,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,58; 55,22</t>
+          <t>38,52; 55,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,69; 65,69</t>
+          <t>49,41; 66,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,85; 60,77</t>
+          <t>45,81; 61,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>84,24; 93,79</t>
+          <t>84,41; 93,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38,85; 51,94</t>
+          <t>39,43; 52,23</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44,2; 56,78</t>
+          <t>44,04; 56,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43,84; 55,62</t>
+          <t>43,86; 55,38</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>85,81; 92,59</t>
+          <t>85,88; 92,59</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40,5; 58,93</t>
+          <t>39,45; 58,86</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>42,81; 65,13</t>
+          <t>41,45; 64,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34,78; 55,81</t>
+          <t>34,49; 55,04</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85,51; 96,58</t>
+          <t>85,18; 96,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44,4; 63,27</t>
+          <t>43,6; 63,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,22; 59,38</t>
+          <t>40,46; 59,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,45; 52,39</t>
+          <t>31,94; 51,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>83,36; 96,84</t>
+          <t>84,08; 96,76</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>45,17; 58,57</t>
+          <t>45,35; 58,93</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43,85; 58,42</t>
+          <t>43,21; 58,5</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>35,98; 50,23</t>
+          <t>36,1; 49,63</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>86,93; 95,85</t>
+          <t>86,94; 95,66</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>36,58; 43,5</t>
+          <t>35,87; 43,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>43,08; 50,23</t>
+          <t>43,1; 50,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38,77; 45,77</t>
+          <t>39,04; 45,8</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93,67; 96,47</t>
+          <t>93,72; 96,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>39,43; 46,47</t>
+          <t>39,46; 46,14</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,32; 51,2</t>
+          <t>44,35; 51,5</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,7; 44,31</t>
+          <t>37,72; 44,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>92,9; 96,04</t>
+          <t>92,97; 96,06</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,97; 43,98</t>
+          <t>39,06; 43,82</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45,04; 50,1</t>
+          <t>44,77; 49,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39,14; 44,12</t>
+          <t>39,3; 44,25</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,85; 95,89</t>
+          <t>93,79; 95,93</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas con enfermedades crónicas (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>24375</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>26165</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>26492</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>102640</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>24725</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>24976</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>30542</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>134602</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>49100</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>51141</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>57034</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>237241</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>17944; 31681</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20047; 32156</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>20177; 33090</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>99028; 103920</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>18524; 31732</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>18951; 32326</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>23898; 37966</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>131170; 136291</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>39722; 58595</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>41245; 59568</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>47875; 67726</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>232628; 239502</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>30298</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>28088</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>28738</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>92255</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>31558</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>30859</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>38456</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>94045</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>61856</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>58947</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>67195</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>186300</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>23546; 37270</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>21607; 34597</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>21648; 35947</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>87951; 93930</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>25714; 38306</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>24510; 37845</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>30432; 46089</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>90152; 95573</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>52085; 71328</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>49516; 68623</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>57833; 77563</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>181488; 188947</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>17110</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>31390</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>18465</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>48301</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>28447</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>27600</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>22846</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>61748</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>45557</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>58990</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>41311</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>110049</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>12202; 23806</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>24651; 37815</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>13290; 24137</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>43605; 51042</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>22449; 35204</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>21182; 34611</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>17257; 29153</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>56456; 63853</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>37259; 54928</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>49620; 68383</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>33909; 50302</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>103861; 113570</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>537</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>60346</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>66659</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>74255</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>212648</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>62613</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>86016</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>60288</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>206506</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>122959</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>152675</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>134543</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>419154</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>51250; 71559</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>58030; 75487</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>64691; 85718</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>206892; 215946</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>52923; 71969</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>74989; 95423</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>50373; 70506</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>198947; 211774</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>110183; 136697</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>138746; 166619</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>120581; 149525</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>408986; 425690</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>30590</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>41303</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>47041</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>107134</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>39796</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>52480</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>53234</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>146157</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>70386</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>93783</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>100275</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>253291</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>23921; 37407</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>33276; 49878</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>39094; 55231</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>100324; 111590</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>32561; 46821</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>45459; 61154</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>45418; 61001</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>137272; 152432</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>60580; 80259</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>81670; 104661</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>88041; 111175</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>242216; 261141</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>37426</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>28790</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>27025</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>63541</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>39094</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>36450</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>28411</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>66365</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>76520</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>65240</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>55436</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>129906</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>29535; 44070</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>22346; 34598</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>20811; 33206</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>58684; 66331</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>31561; 45782</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>29955; 43796</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>21662; 35072</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>60540; 69668</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>66788; 86786</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>55287; 74853</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>46271; 63602</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>122501; 134784</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>690</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>1788</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>200145</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>222394</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>222017</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>626519</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>226233</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>258381</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>233777</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>709422</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>426378</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>480775</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>455794</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>1335941</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>180297; 216629</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>205564; 239769</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>204592; 240017</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>616814; 635374</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>208567; 243856</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>238277; 276695</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>215072; 252716</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>696560; 719678</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>402775; 451833</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>454125; 506605</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>430010; 484228</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>1319988; 1350052</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2A_enfcro_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,3; 39,38</t>
+          <t>22,9; 38,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,75; 52,52</t>
+          <t>32,6; 53,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>31,12; 51,04</t>
+          <t>30,58; 51,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94,8; 99,48</t>
+          <t>94,53; 99,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,86; 44,3</t>
+          <t>25,44; 43,12</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,82; 44,04</t>
+          <t>25,62; 44,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,54; 48,52</t>
+          <t>30,14; 48,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>95,81; 99,55</t>
+          <t>95,22; 99,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,12; 38,53</t>
+          <t>26,22; 38,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,64; 44,25</t>
+          <t>30,8; 45,1</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33,46; 47,33</t>
+          <t>33,72; 46,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,38; 99,23</t>
+          <t>96,71; 99,28</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,28; 54,26</t>
+          <t>34,84; 54,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>33,05; 52,92</t>
+          <t>32,43; 52,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,3; 43,67</t>
+          <t>27,12; 43,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92,89; 99,21</t>
+          <t>92,76; 99,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>38,1; 56,76</t>
+          <t>36,84; 57,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,77; 55,23</t>
+          <t>34,72; 53,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,7; 49,52</t>
+          <t>33,32; 49,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>94,33; 100,0</t>
+          <t>94,02; 100,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,25; 52,38</t>
+          <t>38,04; 51,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,98; 51,25</t>
+          <t>36,9; 51,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,98; 44,23</t>
+          <t>32,13; 44,01</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>95,39; 99,31</t>
+          <t>95,08; 99,31</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,95; 40,87</t>
+          <t>20,62; 40,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,06; 56,84</t>
+          <t>37,18; 57,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,0; 49,04</t>
+          <t>27,72; 48,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>84,08; 98,42</t>
+          <t>83,35; 97,92</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,74; 41,94</t>
+          <t>26,48; 41,84</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,17; 50,93</t>
+          <t>31,69; 50,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,29; 47,78</t>
+          <t>28,25; 47,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>88,42; 100,0</t>
+          <t>90,07; 100,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,2; 38,63</t>
+          <t>26,67; 39,21</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>36,9; 50,85</t>
+          <t>37,03; 51,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,76; 45,63</t>
+          <t>30,19; 45,4</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>89,76; 98,15</t>
+          <t>89,4; 98,06</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,87; 47,3</t>
+          <t>33,81; 46,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,52; 55,31</t>
+          <t>41,26; 55,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,02; 51,7</t>
+          <t>39,26; 51,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94,55; 98,68</t>
+          <t>94,7; 98,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,62; 48,44</t>
+          <t>35,12; 49,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,47; 59,14</t>
+          <t>46,3; 59,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,48; 41,26</t>
+          <t>29,49; 40,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91,15; 97,02</t>
+          <t>91,13; 96,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,75; 45,59</t>
+          <t>36,55; 45,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46,58; 55,94</t>
+          <t>46,78; 56,08</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,81; 44,41</t>
+          <t>35,48; 44,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,57; 97,39</t>
+          <t>93,7; 97,35</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,61; 54,12</t>
+          <t>34,79; 53,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,61; 53,37</t>
+          <t>35,53; 52,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,49; 54,37</t>
+          <t>38,63; 54,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84,0; 93,44</t>
+          <t>84,42; 93,45</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,52; 55,39</t>
+          <t>38,21; 55,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,41; 66,47</t>
+          <t>48,27; 65,44</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,81; 61,52</t>
+          <t>45,93; 62,77</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>84,41; 93,74</t>
+          <t>83,93; 93,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,43; 52,23</t>
+          <t>39,01; 51,96</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44,04; 56,43</t>
+          <t>44,57; 56,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43,86; 55,38</t>
+          <t>43,82; 55,18</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>85,88; 92,59</t>
+          <t>85,96; 92,38</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,45; 58,86</t>
+          <t>39,84; 59,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41,45; 64,18</t>
+          <t>41,97; 64,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34,49; 55,04</t>
+          <t>34,06; 56,09</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85,18; 96,28</t>
+          <t>85,42; 96,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>43,6; 63,24</t>
+          <t>44,98; 62,76</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>40,46; 59,15</t>
+          <t>39,8; 59,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,94; 51,71</t>
+          <t>31,93; 52,11</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>84,08; 96,76</t>
+          <t>83,89; 96,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>45,35; 58,93</t>
+          <t>44,95; 58,78</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>43,21; 58,5</t>
+          <t>44,03; 57,78</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36,1; 49,63</t>
+          <t>36,49; 50,8</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>86,94; 95,66</t>
+          <t>86,34; 95,44</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>35,87; 43,1</t>
+          <t>35,91; 43,3</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>43,1; 50,27</t>
+          <t>42,91; 50,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39,04; 45,8</t>
+          <t>38,74; 45,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93,72; 96,54</t>
+          <t>93,61; 96,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>39,46; 46,14</t>
+          <t>39,5; 46,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,35; 51,5</t>
+          <t>44,26; 51,64</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,72; 44,32</t>
+          <t>37,22; 44,03</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>92,97; 96,06</t>
+          <t>92,96; 96,09</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>39,06; 43,82</t>
+          <t>38,85; 43,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44,77; 49,95</t>
+          <t>44,94; 50,07</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39,3; 44,25</t>
+          <t>39,22; 43,87</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,79; 95,93</t>
+          <t>93,72; 95,87</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>17944; 31681</t>
+          <t>18426; 31077</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20047; 32156</t>
+          <t>19955; 32695</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20177; 33090</t>
+          <t>19824; 33172</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>99028; 103920</t>
+          <t>98746; 103938</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18524; 31732</t>
+          <t>18222; 30892</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18951; 32326</t>
+          <t>18804; 32444</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23898; 37966</t>
+          <t>23588; 38171</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>131170; 136291</t>
+          <t>130363; 136254</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39722; 58595</t>
+          <t>39874; 58280</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41245; 59568</t>
+          <t>41473; 60719</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>47875; 67726</t>
+          <t>48245; 66963</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>232628; 239502</t>
+          <t>233419; 239627</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23546; 37270</t>
+          <t>23928; 37296</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21607; 34597</t>
+          <t>21202; 34503</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21648; 35947</t>
+          <t>22319; 35917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87951; 93930</t>
+          <t>87828; 93933</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25714; 38306</t>
+          <t>24865; 38570</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24510; 37845</t>
+          <t>23790; 36978</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>30432; 46089</t>
+          <t>31014; 46248</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>90152; 95573</t>
+          <t>89856; 95573</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>52085; 71328</t>
+          <t>51806; 70362</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49516; 68623</t>
+          <t>49411; 69386</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57833; 77563</t>
+          <t>56341; 77182</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>181488; 188947</t>
+          <t>180899; 188945</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12202; 23806</t>
+          <t>12008; 23621</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24651; 37815</t>
+          <t>24736; 38111</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13290; 24137</t>
+          <t>13643; 23941</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43605; 51042</t>
+          <t>43228; 50782</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22449; 35204</t>
+          <t>22225; 35124</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21182; 34611</t>
+          <t>21537; 34476</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17257; 29153</t>
+          <t>17236; 29127</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>56456; 63853</t>
+          <t>57511; 63853</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37259; 54928</t>
+          <t>37916; 55754</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49620; 68383</t>
+          <t>49807; 68971</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33909; 50302</t>
+          <t>33274; 50042</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>103861; 113570</t>
+          <t>103454; 113466</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51250; 71559</t>
+          <t>51154; 71098</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58030; 75487</t>
+          <t>56316; 75847</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>64691; 85718</t>
+          <t>65099; 85824</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>206892; 215946</t>
+          <t>207227; 216091</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52923; 71969</t>
+          <t>52174; 73145</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>74989; 95423</t>
+          <t>74707; 96606</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50373; 70506</t>
+          <t>50390; 70016</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>198947; 211774</t>
+          <t>198907; 211478</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>110183; 136697</t>
+          <t>109613; 136922</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>138746; 166619</t>
+          <t>139328; 167035</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>120581; 149525</t>
+          <t>119458; 148335</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>408986; 425690</t>
+          <t>409570; 425520</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>23921; 37407</t>
+          <t>24048; 37085</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33276; 49878</t>
+          <t>33206; 49125</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39094; 55231</t>
+          <t>39245; 55668</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100324; 111590</t>
+          <t>100826; 111604</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32561; 46821</t>
+          <t>32301; 47328</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>45459; 61154</t>
+          <t>44412; 60212</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45418; 61001</t>
+          <t>45540; 62242</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>137272; 152432</t>
+          <t>136492; 152293</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>60580; 80259</t>
+          <t>59933; 79835</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>81670; 104661</t>
+          <t>82653; 104345</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88041; 111175</t>
+          <t>87953; 110765</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>242216; 261141</t>
+          <t>242452; 260557</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>29535; 44070</t>
+          <t>29824; 44352</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22346; 34598</t>
+          <t>22629; 34982</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20811; 33206</t>
+          <t>20553; 33842</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>58684; 66331</t>
+          <t>58853; 66649</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>31561; 45782</t>
+          <t>32563; 45433</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29955; 43796</t>
+          <t>29466; 44009</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21662; 35072</t>
+          <t>21654; 35345</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>60540; 69668</t>
+          <t>60407; 69627</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>66788; 86786</t>
+          <t>66196; 86558</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>55287; 74853</t>
+          <t>56331; 73932</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46271; 63602</t>
+          <t>46769; 65105</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>122501; 134784</t>
+          <t>121650; 134472</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>180297; 216629</t>
+          <t>180505; 217675</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>205564; 239769</t>
+          <t>204644; 239956</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>204592; 240017</t>
+          <t>203032; 240353</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>616814; 635374</t>
+          <t>616128; 634767</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>208567; 243856</t>
+          <t>208778; 245146</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>238277; 276695</t>
+          <t>237805; 277451</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>215072; 252716</t>
+          <t>212206; 251055</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>696560; 719678</t>
+          <t>696483; 719961</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>402775; 451833</t>
+          <t>400611; 453544</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>454125; 506605</t>
+          <t>455793; 507891</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>430010; 484228</t>
+          <t>429128; 480035</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1319988; 1350052</t>
+          <t>1318983; 1349203</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2A_enfcro_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P2A_enfcro_R-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>34,51%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>34,02%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>39,03%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>98,27%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>30,3%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>42,74%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>40,86%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>98,26%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>34,51%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,02%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>39,03%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,9; 38,63</t>
+          <t>25,68; 44,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>32,6; 53,41</t>
+          <t>25,72; 45,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>30,58; 51,17</t>
+          <t>29,79; 48,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>94,53; 99,5</t>
+          <t>95,49; 99,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>25,44; 43,12</t>
+          <t>22,03; 39,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,62; 44,2</t>
+          <t>31,33; 52,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,14; 48,78</t>
+          <t>30,42; 51,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>95,22; 99,52</t>
+          <t>94,66; 99,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>26,22; 38,32</t>
+          <t>26,51; 38,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30,8; 45,1</t>
+          <t>32,14; 46,16</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33,72; 46,8</t>
+          <t>32,54; 46,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>96,71; 99,28</t>
+          <t>96,36; 99,28</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>46,76%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>45,03%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>41,32%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>98,41%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>44,11%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>42,96%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>34,91%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>46,76%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>45,03%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>41,32%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,85%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>34,84; 54,3</t>
+          <t>36,85; 56,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32,43; 52,77</t>
+          <t>36,09; 55,68</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27,12; 43,64</t>
+          <t>32,2; 49,26</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>92,76; 99,21</t>
+          <t>94,23; 100,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,84; 57,15</t>
+          <t>35,1; 54,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,72; 53,96</t>
+          <t>33,03; 53,47</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,32; 49,69</t>
+          <t>26,71; 44,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>94,02; 100,0</t>
+          <t>92,97; 99,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,04; 51,67</t>
+          <t>38,55; 51,92</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,9; 51,82</t>
+          <t>37,32; 51,33</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32,13; 44,01</t>
+          <t>32,61; 44,94</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>95,08; 99,31</t>
+          <t>95,21; 99,33</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>33,89%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>40,61%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37,45%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>96,64%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>29,38%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>47,19%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>37,51%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>93,14%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>33,89%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>40,61%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>37,45%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,05%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,62; 40,55</t>
+          <t>25,96; 42,94</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,18; 57,29</t>
+          <t>31,31; 50,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27,72; 48,64</t>
+          <t>28,36; 47,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>83,35; 97,92</t>
+          <t>89,34; 100,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>26,48; 41,84</t>
+          <t>21,35; 40,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>31,69; 50,73</t>
+          <t>37,23; 57,56</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,25; 47,74</t>
+          <t>27,86; 48,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>90,07; 100,0</t>
+          <t>84,39; 98,32</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>26,67; 39,21</t>
+          <t>26,06; 39,39</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>37,03; 51,28</t>
+          <t>36,64; 51,56</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30,19; 45,4</t>
+          <t>30,46; 45,18</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>89,4; 98,06</t>
+          <t>89,74; 97,8</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>42,15%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>53,31%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>35,28%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>94,46%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>39,89%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>48,84%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>44,79%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>97,18%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>42,15%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>53,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,28%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,59%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>33,81; 46,99</t>
+          <t>35,53; 48,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41,26; 55,57</t>
+          <t>47,1; 59,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,26; 51,76</t>
+          <t>29,64; 41,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94,7; 98,75</t>
+          <t>90,76; 96,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,12; 49,24</t>
+          <t>33,43; 46,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,3; 59,87</t>
+          <t>42,54; 56,2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,49; 40,97</t>
+          <t>38,47; 51,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>91,13; 96,89</t>
+          <t>93,93; 98,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>36,55; 45,66</t>
+          <t>36,38; 45,44</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46,78; 56,08</t>
+          <t>46,42; 55,64</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35,48; 44,06</t>
+          <t>35,52; 44,02</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,7; 97,35</t>
+          <t>93,43; 97,18</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>47,08%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>57,04%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>53,69%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>89,83%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>44,25%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>44,2%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>46,31%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>89,71%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>47,08%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>57,04%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>53,69%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>89,8%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,79; 53,65</t>
+          <t>38,58; 55,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>35,53; 52,57</t>
+          <t>48,69; 65,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>38,63; 54,8</t>
+          <t>44,85; 60,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84,42; 93,45</t>
+          <t>84,7; 93,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>38,21; 55,99</t>
+          <t>35,28; 54,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>48,27; 65,44</t>
+          <t>35,99; 52,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>45,93; 62,77</t>
+          <t>38,25; 53,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>83,93; 93,65</t>
+          <t>84,95; 93,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,01; 51,96</t>
+          <t>38,85; 51,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>44,57; 56,26</t>
+          <t>44,2; 56,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>43,82; 55,18</t>
+          <t>43,84; 55,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>85,96; 92,38</t>
+          <t>86,06; 92,76</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>54,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>49,23%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>41,89%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>92,85%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>49,99%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>53,4%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>44,79%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>92,23%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>54,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>49,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>41,89%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,62%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>39,84; 59,24</t>
+          <t>44,4; 63,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>41,97; 64,89</t>
+          <t>40,22; 59,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34,06; 56,09</t>
+          <t>32,45; 52,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>85,42; 96,74</t>
+          <t>84,67; 97,06</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>44,98; 62,76</t>
+          <t>40,5; 58,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>39,8; 59,44</t>
+          <t>42,81; 65,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,93; 52,11</t>
+          <t>34,78; 55,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>83,89; 96,7</t>
+          <t>85,51; 96,59</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>44,95; 58,78</t>
+          <t>45,17; 58,57</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44,03; 57,78</t>
+          <t>43,85; 58,42</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>36,49; 50,8</t>
+          <t>35,98; 50,23</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>86,34; 95,44</t>
+          <t>87,75; 96,17</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>42,8%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>48,09%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>41,0%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>94,69%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>39,82%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>46,63%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>42,36%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>95,19%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>42,8%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>48,09%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>41,0%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>35,91; 43,3</t>
+          <t>39,43; 46,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>42,91; 50,31</t>
+          <t>44,32; 51,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38,74; 45,86</t>
+          <t>37,7; 44,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>93,61; 96,45</t>
+          <t>92,91; 96,06</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>39,5; 46,38</t>
+          <t>36,58; 43,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>44,26; 51,64</t>
+          <t>43,08; 50,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,22; 44,03</t>
+          <t>38,77; 45,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>92,96; 96,09</t>
+          <t>93,49; 96,25</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>38,85; 43,98</t>
+          <t>38,97; 43,98</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44,94; 50,07</t>
+          <t>45,04; 50,1</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39,22; 43,87</t>
+          <t>39,14; 44,12</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>93,72; 95,87</t>
+          <t>93,72; 95,86</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>153</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>24725</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>24976</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>30542</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>120452</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>24375</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>26165</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>26492</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>102640</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>24725</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>24976</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>30542</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>134602</t>
+          <t>100953</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>237241</t>
+          <t>221407</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18426; 31077</t>
+          <t>18398; 31674</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19955; 32695</t>
+          <t>18878; 33031</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19824; 33172</t>
+          <t>23315; 37611</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>98746; 103938</t>
+          <t>117049; 122045</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>18222; 30892</t>
+          <t>17727; 31696</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18804; 32444</t>
+          <t>19178; 32071</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23588; 38171</t>
+          <t>19723; 33281</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>130363; 136254</t>
+          <t>97435; 102552</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39874; 58280</t>
+          <t>40324; 58711</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>41473; 60719</t>
+          <t>43270; 62152</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48245; 66963</t>
+          <t>46563; 65829</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>233419; 239627</t>
+          <t>217287; 223886</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>43</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>138</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>31558</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>30859</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>38456</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>89945</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>30298</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>28088</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>28738</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>92255</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>31558</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>30859</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>38456</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>94045</t>
+          <t>93961</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>186300</t>
+          <t>183907</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>23928; 37296</t>
+          <t>24869; 38184</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>21202; 34503</t>
+          <t>24733; 38153</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22319; 35917</t>
+          <t>29971; 45843</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>87828; 93933</t>
+          <t>86124; 91398</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24865; 38570</t>
+          <t>24108; 37603</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23790; 36978</t>
+          <t>21592; 34957</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31014; 46248</t>
+          <t>21986; 36240</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89856; 95573</t>
+          <t>89764; 95744</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>51806; 70362</t>
+          <t>52495; 70696</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49411; 69386</t>
+          <t>49969; 68735</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>56341; 77182</t>
+          <t>57199; 78821</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>180899; 188945</t>
+          <t>178933; 186693</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>71</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>82</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>28447</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>27600</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>22846</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>55028</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>17110</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>31390</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>18465</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>48301</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>28447</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>27600</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>22846</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>61748</t>
+          <t>49925</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>110049</t>
+          <t>104953</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>12008; 23621</t>
+          <t>21789; 36050</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24736; 38111</t>
+          <t>21279; 34526</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>13643; 23941</t>
+          <t>17300; 29082</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>43228; 50782</t>
+          <t>50869; 56941</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>22225; 35124</t>
+          <t>12434; 23440</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>21537; 34476</t>
+          <t>24769; 38292</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17236; 29127</t>
+          <t>13712; 23930</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>57511; 63853</t>
+          <t>45135; 52583</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>37916; 55754</t>
+          <t>37048; 56012</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49807; 68971</t>
+          <t>49280; 69337</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33274; 50042</t>
+          <t>33575; 49804</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>103454; 113466</t>
+          <t>99099; 107993</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>112</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>268</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>62613</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>86016</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>60288</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>190760</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>60346</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>66659</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>74255</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>212648</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>62613</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>86016</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>60288</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>206506</t>
+          <t>174021</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>419154</t>
+          <t>364781</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>51154; 71098</t>
+          <t>52787; 71836</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>56316; 75847</t>
+          <t>76007; 96355</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>65099; 85824</t>
+          <t>50654; 70357</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>207227; 216091</t>
+          <t>183284; 195771</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52174; 73145</t>
+          <t>50581; 70881</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>74707; 96606</t>
+          <t>58060; 76699</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50390; 70016</t>
+          <t>63783; 85067</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>198907; 211478</t>
+          <t>168748; 176870</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>109613; 136922</t>
+          <t>109094; 136248</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>139328; 167035</t>
+          <t>138264; 165729</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>119458; 148335</t>
+          <t>119600; 148214</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>409570; 425520</t>
+          <t>356546; 370840</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>160</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>39796</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>52480</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>53234</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>133168</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>30590</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>41303</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>47041</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>107134</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>39796</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>52480</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>53234</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>146157</t>
+          <t>106565</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>253291</t>
+          <t>239733</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>24048; 37085</t>
+          <t>32612; 46674</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>33206; 49125</t>
+          <t>44797; 60444</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39245; 55668</t>
+          <t>44474; 60256</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>100826; 111604</t>
+          <t>125555; 139174</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>32301; 47328</t>
+          <t>24389; 37638</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>44412; 60212</t>
+          <t>33631; 49126</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>45540; 62242</t>
+          <t>38855; 54805</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>136492; 152293</t>
+          <t>100863; 111231</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>59933; 79835</t>
+          <t>59691; 79809</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>82653; 104345</t>
+          <t>81969; 105303</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>87953; 110765</t>
+          <t>88010; 111649</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>242452; 260557</t>
+          <t>229768; 247637</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>41</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>91</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>39094</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>36450</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>28411</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>63401</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>37426</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>28790</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>27025</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>63541</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>39094</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>36450</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>28411</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>66365</t>
+          <t>65007</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>129906</t>
+          <t>128409</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>29824; 44352</t>
+          <t>32145; 45801</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>22629; 34982</t>
+          <t>29781; 43962</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20553; 33842</t>
+          <t>22010; 35534</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>58853; 66649</t>
+          <t>57820; 66283</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>32563; 45433</t>
+          <t>30324; 44120</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>29466; 44009</t>
+          <t>23082; 35114</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21654; 35345</t>
+          <t>20985; 33672</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>60407; 69627</t>
+          <t>60159; 67960</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>66196; 86558</t>
+          <t>66517; 86251</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>56331; 73932</t>
+          <t>56110; 74743</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46769; 65105</t>
+          <t>46110; 64379</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>121650; 134472</t>
+          <t>121664; 133340</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>296</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>320</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>329</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>881</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>370</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>340</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>907</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>226233</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>258381</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>233777</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>652755</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>200145</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>222394</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>222017</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>626519</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>226233</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>258381</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>233777</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>709422</t>
+          <t>590433</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1335941</t>
+          <t>1243189</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>180505; 217675</t>
+          <t>208384; 245623</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>204644; 239956</t>
+          <t>238150; 275120</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>203032; 240353</t>
+          <t>214954; 252669</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>616128; 634767</t>
+          <t>640485; 662211</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>208778; 245146</t>
+          <t>183891; 218659</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>237805; 277451</t>
+          <t>205485; 239569</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>212206; 251055</t>
+          <t>203176; 239855</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>696483; 719961</t>
+          <t>581250; 598370</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>400611; 453544</t>
+          <t>401909; 453569</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>455793; 507891</t>
+          <t>456874; 508158</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>429128; 480035</t>
+          <t>428295; 482776</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1318983; 1349203</t>
+          <t>1228783; 1256840</t>
         </is>
       </c>
     </row>
